--- a/docs/ValueSet-GoalDescriptionVS-TWLTC.xlsx
+++ b/docs/ValueSet-GoalDescriptionVS-TWLTC.xlsx
@@ -8,13 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -85,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>照顧目標的描述值集，用以表述長期照顧情境中涉及之照顧目標描述內容。本值集比照 US Core Goal Profile 中的 description 元素定義，引用 SNOMED CT 與 LOINC 等術語系統。</t>
+    <t>照顧目標的描述值集，用以表述長期照顧情境中涉及之照顧目標描述內容。本值集列舉臺灣長期照顧情境常用之 SNOMED CT 照顧目標代碼，綁定強度為 extensible，實作者可依需求使用其他 SNOMED CT 或 LOINC 代碼。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,19 +99,103 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>710950005</t>
+  </si>
+  <si>
+    <t>Advancing mobility</t>
+  </si>
+  <si>
+    <t>370885003</t>
+  </si>
+  <si>
+    <t>Manage activities of daily living (ADLS)</t>
+  </si>
+  <si>
+    <t>386373004</t>
+  </si>
+  <si>
+    <t>Nutrition therapy</t>
+  </si>
+  <si>
+    <t>718361005</t>
+  </si>
+  <si>
+    <t>Weight management program</t>
+  </si>
+  <si>
+    <t>278414003</t>
+  </si>
+  <si>
+    <t>Pain management</t>
+  </si>
+  <si>
+    <t>386296001</t>
+  </si>
+  <si>
+    <t>Fall prevention</t>
+  </si>
+  <si>
+    <t>702474001</t>
+  </si>
+  <si>
+    <t>Cognitive rehabilitation therapy</t>
+  </si>
+  <si>
+    <t>5154007</t>
+  </si>
+  <si>
+    <t>Speech therapy</t>
+  </si>
+  <si>
+    <t>385942004</t>
+  </si>
+  <si>
+    <t>Wound care management</t>
+  </si>
+  <si>
+    <t>710054004</t>
+  </si>
+  <si>
+    <t>Maintaining skin integrity</t>
+  </si>
+  <si>
+    <t>385991005</t>
+  </si>
+  <si>
+    <t>Wellness promotion</t>
+  </si>
+  <si>
+    <t>182832007</t>
+  </si>
+  <si>
+    <t>Drug administration</t>
+  </si>
+  <si>
+    <t>430193006</t>
+  </si>
+  <si>
+    <t>Medication reconciliation</t>
+  </si>
+  <si>
+    <t>133921002</t>
+  </si>
+  <si>
+    <t>Emotional support</t>
+  </si>
+  <si>
+    <t>129008009</t>
+  </si>
+  <si>
+    <t>Bowel control</t>
   </si>
   <si>
     <t>System URI</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
 </sst>
 </file>
@@ -376,7 +459,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -387,66 +470,144 @@
       <c r="A1" t="s" s="1">
         <v>28</v>
       </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="B17" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>32</v>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-GoalDescriptionVS-TWLTC.xlsx
+++ b/docs/ValueSet-GoalDescriptionVS-TWLTC.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
